--- a/tests/coeficienteExtLineal1.xlsx
+++ b/tests/coeficienteExtLineal1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t xml:space="preserve">DATOS DE Coeficiente de Extensibilidad Lineal</t>
   </si>
@@ -31,10 +31,10 @@
     <t xml:space="preserve">Rep</t>
   </si>
   <si>
-    <t xml:space="preserve">Longitud Inicial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diámetro de la muestra</t>
+    <t xml:space="preserve">Longitud Inicial (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diámetro de la muestra (mm)</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de Medición</t>
@@ -46,23 +46,109 @@
     <t xml:space="preserve">12.45</t>
   </si>
   <si>
+    <t xml:space="preserve">50.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.38</t>
   </si>
   <si>
+    <t xml:space="preserve">50.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">13.02</t>
   </si>
   <si>
+    <t xml:space="preserve">51.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="hh:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -87,6 +173,13 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -141,7 +234,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -158,8 +251,40 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -182,37 +307,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -285,7 +410,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -336,114 +461,424 @@
       <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>209</v>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>45717</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>0.34375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>45717</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.364583333333333</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>45717</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0.388888888888889</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>45718</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.381944444444444</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>45718</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.402777777777778</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>45718</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.427083333333333</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>45719</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.430555555555556</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>45719</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.451388888888889</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>45719</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0.475694444444444</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>45720</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.354166666666667</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>45720</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.378472222222222</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E14" s="7" t="n">
+        <v>45721</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.385416666666667</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="E15" s="7" t="n">
+        <v>45721</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0.40625</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>45722</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.347222222222222</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>45722</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.371527777777778</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>45723</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.423611111111111</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>45723</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>212</v>
-      </c>
+      <c r="B20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>45724</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>45724</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/coeficienteExtLineal1.xlsx
+++ b/tests/coeficienteExtLineal1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\analisys\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\AnaliSys\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8B998-4509-4766-9FA0-6E4AC4422FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D64266A-7DD4-4F76-B931-D7FD2091C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -524,20 +524,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="27.5546875" customWidth="1"/>
-    <col min="5" max="5" width="29.77734375" customWidth="1"/>
-    <col min="6" max="6" width="26.77734375" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" customWidth="1"/>
-    <col min="8" max="8" width="24.6640625" customWidth="1"/>
-    <col min="9" max="9" width="32.33203125" customWidth="1"/>
-    <col min="10" max="10" width="29.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" customWidth="1"/>
+    <col min="7" max="7" width="29.42578125" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="32.28515625" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="25.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -559,7 +559,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -595,7 +595,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>1001</v>
       </c>
@@ -627,7 +627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1002</v>
       </c>
@@ -659,7 +659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1003</v>
       </c>
@@ -691,7 +691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>1004</v>
       </c>
@@ -723,7 +723,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1005</v>
       </c>
@@ -755,7 +755,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1006</v>
       </c>
@@ -787,7 +787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>1007</v>
       </c>
@@ -819,7 +819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>1008</v>
       </c>
@@ -851,7 +851,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>1009</v>
       </c>
@@ -883,7 +883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>1010</v>
       </c>
@@ -915,7 +915,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>1011</v>
       </c>
@@ -947,7 +947,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>1012</v>
       </c>
@@ -979,7 +979,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>1013</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>1014</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>1015</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>1016</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>1017</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1018</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1018</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1019</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1020</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1021</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1022</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1023</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1024</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1025</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1026</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1027</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1028</v>
       </c>
@@ -1525,7 +1525,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
